--- a/Tables/output.xlsx
+++ b/Tables/output.xlsx
@@ -470,19 +470,19 @@
         <v>-0.115787711999745</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004719622344265627</v>
+        <v>-0.003653582663624462</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0003103362228952244</v>
+        <v>-0.00196625161560518</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.925508550897979</v>
+        <v>-1.918316325774458</v>
       </c>
       <c r="F2" t="n">
-        <v>1.95195409292641</v>
+        <v>1.921926267478224</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.9064</v>
       </c>
     </row>
     <row r="3">
@@ -495,19 +495,19 @@
         <v>-1.182483644484863</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.001199914436588109</v>
+        <v>-0.007229108989866388</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.00924350617327304</v>
+        <v>-0.02157847145322379</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.557275012164553</v>
+        <v>-1.544448164649104</v>
       </c>
       <c r="F3" t="n">
-        <v>1.60796632512222</v>
+        <v>1.582824169947167</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1478</v>
+        <v>0.1449</v>
       </c>
     </row>
     <row r="4">

--- a/Tables/output.xlsx
+++ b/Tables/output.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAAR" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AAR" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,139 +425,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Valós</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Átlag</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Medián</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>p-érték</t>
-        </is>
+      <c r="B1" s="1" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C1" s="1" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D1" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CAAR[-1,1]</t>
+          <t>Trump részvények</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.115787711999745</v>
+        <v>-1.537625709580799</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.003653582663624462</v>
+        <v>1.385256739781215</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00196625161560518</v>
+        <v>0.1679356867120909</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.918316325774458</v>
+        <v>3.499659232164717</v>
       </c>
       <c r="F2" t="n">
-        <v>1.921926267478224</v>
+        <v>-1.652262706143617</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9064</v>
+        <v>2.828325664951182</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5.332748201676536</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.9334744207565655</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CAAR[0,1]</t>
+          <t>Harris részvények</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.182483644484863</v>
+        <v>-1.505756969184022</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.007229108989866388</v>
+        <v>1.635703673054116</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02157847145322379</v>
+        <v>0.4718015913673128</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.544448164649104</v>
+        <v>-6.19969389241612</v>
       </c>
       <c r="F3" t="n">
-        <v>1.582824169947167</v>
+        <v>-0.2124851468585694</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1449</v>
+        <v>0.5453917017791796</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-1.610825937743028</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-2.393022406333674</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CAAR[1,3]</t>
+          <t>Tech részvények</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.7369935532877838</v>
+        <v>-0.9535527779647102</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.00381580439292437</v>
+        <v>-0.4503720284355821</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.003312215925577594</v>
+        <v>-0.9017697185032425</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.252272351261925</v>
+        <v>1.215235474127688</v>
       </c>
       <c r="F4" t="n">
-        <v>2.183904256126337</v>
+        <v>-1.485546932463468</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5158</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>CAAR[1,5]</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>-0.4474648098159981</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.008171336215119217</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.02114672619897275</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-2.738021529154462</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.746697430324348</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.7479</v>
+        <v>-2.087902072480699</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7031247015743661</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8876499217344634</v>
       </c>
     </row>
   </sheetData>
